--- a/base/StructureDefinition-SGCodeSystem.xlsx
+++ b/base/StructureDefinition-SGCodeSystem.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2657" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="420">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>csd-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}
-csd-1:Within a code system definition, all the codes SHALL be unique {concept.code.combine($this.descendants().concept.code).isDistinct()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}scs-1:If a codesystem contains nested concepts, it must specify hierarchyMeaning {concept.concept.exists() implies hierarchyMeaning.exists()}scs-2:If a codesystem contains example, fragment, or complete content, it must have at least one concept {content in ( 'example' | 'fragment' | 'complete' ) implies concept.exists()}</t>
+csd-1:Within a code system definition, all the codes SHALL be unique {concept.code.combine($this.descendants().concept.code).isDistinct()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}scs-1:If a codesystem contains nested concepts, it must specify hierarchyMeaning {concept.concept.exists() implies hierarchyMeaning.exists()}shr-1:If knowledge capabilities are stated, they SHALL include shareable {extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').exists() implies extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').where(value = 'shareable').exists()}scs-2:If a codesystem contains example, fragment, or complete content, it must have at least one concept {content in ( 'example' | 'fragment' | 'complete' ) implies concept.exists()}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -456,6 +456,10 @@
     <t>Defines a knowledge capability afforded by this knowledge artifact.</t>
   </si>
   <si>
+    <t>ele-1
+shr-1</t>
+  </si>
+  <si>
     <t>CodeSystem.extension:versionAlgorithm</t>
   </si>
   <si>
@@ -475,6 +479,10 @@
     <t>If set as a string, this is a FHIRPath expression that has two additional context variables passed in - %version1 and %version2 and will return a negative number if version1 is newer, a positive number if version2 and a 0 if the version ordering can't be successfully be determined.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>CodeSystem.extension:versionPolicy</t>
   </si>
   <si>
@@ -489,6 +497,22 @@
   </si>
   <si>
     <t>Defines the versioning policy of the artifact.</t>
+  </si>
+  <si>
+    <t>CodeSystem.extension:webSource</t>
+  </si>
+  <si>
+    <t>webSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {web-source}
+</t>
+  </si>
+  <si>
+    <t>web-source</t>
+  </si>
+  <si>
+    <t>Where a human readable web page describing the resource can be found, if it's at a different location to the canonical URL itself.</t>
   </si>
   <si>
     <t>CodeSystem.modifierExtension</t>
@@ -800,7 +824,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -861,7 +885,7 @@
     <t>CodeSystem.valueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ValueSet)
+    <t xml:space="preserve">canonical(ValueSet|4.0.1)
 </t>
   </si>
   <si>
@@ -947,7 +971,7 @@
     <t>CodeSystem.supplements</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(CodeSystem)
+    <t xml:space="preserve">canonical(CodeSystem|4.0.1)
 </t>
   </si>
   <si>
@@ -1241,7 +1265,7 @@
     <t>Details of how a designation would be used.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/designation-use</t>
+    <t>http://hl7.org/fhir/ValueSet/designation-use|4.0.1</t>
   </si>
   <si>
     <t>CodeSystem.concept.designation.value</t>
@@ -1616,20 +1640,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN73"/>
+  <dimension ref="A1:AN74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.63671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.63671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.65234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.98046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.98046875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.2890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="41.4296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="36.44140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1638,26 +1662,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="112.1640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.59765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.41796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="99.73046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.95703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.05078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.67578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2686,7 +2710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>136</v>
       </c>
@@ -2782,7 +2806,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>135</v>
@@ -2800,15 +2824,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>128</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -2830,16 +2854,16 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2898,7 +2922,7 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>135</v>
@@ -2918,13 +2942,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>128</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -2937,7 +2961,7 @@
         <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -2946,13 +2970,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3012,7 +3036,7 @@
         <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>135</v>
@@ -3030,48 +3054,46 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>20</v>
       </c>
@@ -3119,7 +3141,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3128,13 +3150,13 @@
         <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>135</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
@@ -3155,38 +3177,38 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I14" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3235,34 +3257,34 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>166</v>
       </c>
@@ -3275,13 +3297,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
@@ -3290,19 +3312,19 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3357,7 +3379,7 @@
         <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
@@ -3369,21 +3391,21 @@
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AM15" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="AN15" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3391,13 +3413,13 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
@@ -3406,18 +3428,20 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3465,13 +3489,13 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
@@ -3486,13 +3510,13 @@
         <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AN16" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>181</v>
       </c>
@@ -3520,20 +3544,18 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O17" t="s" s="2">
         <v>185</v>
       </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3590,7 +3612,7 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>97</v>
@@ -3599,21 +3621,21 @@
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3636,18 +3658,20 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3695,7 +3719,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3704,7 +3728,7 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>97</v>
@@ -3713,7 +3737,7 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>20</v>
@@ -3722,12 +3746,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3744,22 +3768,22 @@
         <v>86</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3785,13 +3809,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3809,10 +3833,10 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>77</v>
@@ -3827,21 +3851,21 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3858,26 +3882,24 @@
         <v>86</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -3901,13 +3923,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3925,10 +3947,10 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>77</v>
@@ -3952,7 +3974,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>208</v>
       </c>
@@ -3961,17 +3983,17 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
@@ -3980,18 +4002,20 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4057,10 +4081,10 @@
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -4068,24 +4092,24 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -4094,20 +4118,18 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O22" t="s" s="2">
         <v>220</v>
       </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4155,7 +4177,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4182,7 +4204,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>223</v>
       </c>
@@ -4195,13 +4217,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -4210,18 +4232,20 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4275,7 +4299,7 @@
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4290,7 +4314,7 @@
         <v>228</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4298,30 +4322,30 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>231</v>
@@ -4383,13 +4407,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4398,7 +4422,7 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>235</v>
@@ -4410,7 +4434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>236</v>
       </c>
@@ -4419,39 +4443,37 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O25" t="s" s="2">
         <v>241</v>
       </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4505,7 +4527,7 @@
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4514,7 +4536,7 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>242</v>
@@ -4565,7 +4587,9 @@
       <c r="N26" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4589,13 +4613,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4631,7 +4655,7 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4642,10 +4666,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4656,7 +4680,7 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4665,19 +4689,19 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4703,13 +4727,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>20</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4727,13 +4751,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -4745,25 +4769,25 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4782,7 +4806,7 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>260</v>
@@ -4793,9 +4817,7 @@
       <c r="N28" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="O28" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4843,7 +4865,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4861,13 +4883,13 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AM28" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AN28" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -4879,37 +4901,39 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -4975,21 +4999,21 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4997,13 +5021,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -5012,16 +5036,16 @@
         <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5071,7 +5095,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5100,10 +5124,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5117,7 +5141,7 @@
         <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
@@ -5126,16 +5150,16 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>105</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5161,13 +5185,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>278</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>279</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5185,7 +5209,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5194,7 +5218,7 @@
         <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>97</v>
@@ -5212,7 +5236,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>281</v>
       </c>
@@ -5221,7 +5245,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>282</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5231,7 +5255,7 @@
         <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
@@ -5240,16 +5264,16 @@
         <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5275,13 +5299,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>20</v>
+        <v>286</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5308,7 +5332,7 @@
         <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>97</v>
@@ -5328,14 +5352,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5354,16 +5378,16 @@
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5413,7 +5437,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5442,10 +5466,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5453,13 +5477,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
@@ -5468,15 +5492,17 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5501,40 +5527,40 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>97</v>
@@ -5552,12 +5578,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5565,13 +5591,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
@@ -5580,7 +5606,7 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>297</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>298</v>
@@ -5588,9 +5614,7 @@
       <c r="M35" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>300</v>
-      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5615,13 +5639,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5639,16 +5663,16 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>97</v>
@@ -5668,10 +5692,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5694,16 +5718,16 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5753,7 +5777,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5782,10 +5806,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5796,7 +5820,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5808,16 +5832,16 @@
         <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5867,13 +5891,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -5896,10 +5920,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5910,7 +5934,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5919,18 +5943,20 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -5979,22 +6005,22 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -6008,21 +6034,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6034,17 +6060,15 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6093,22 +6117,22 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -6122,14 +6146,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>321</v>
+        <v>160</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6142,26 +6166,24 @@
         <v>20</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6209,7 +6231,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6224,7 +6246,7 @@
         <v>135</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6238,42 +6260,46 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6321,22 +6347,22 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -6350,10 +6376,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6361,7 +6387,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>77</v>
@@ -6376,13 +6402,13 @@
         <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6433,10 +6459,10 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>77</v>
@@ -6462,10 +6488,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6473,10 +6499,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6488,13 +6514,13 @@
         <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6521,37 +6547,37 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>334</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AA43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="AG43" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -6574,10 +6600,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6588,7 +6614,7 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6600,13 +6626,13 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6633,13 +6659,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6657,13 +6683,13 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -6686,10 +6712,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6697,10 +6723,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6712,13 +6738,13 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>307</v>
+        <v>182</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6769,13 +6795,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -6798,10 +6824,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6812,7 +6838,7 @@
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6821,16 +6847,16 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6881,22 +6907,22 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>20</v>
@@ -6910,21 +6936,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -6936,17 +6962,15 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -6995,22 +7019,22 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
@@ -7024,14 +7048,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>321</v>
+        <v>160</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7044,26 +7068,24 @@
         <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7111,7 +7133,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7126,7 +7148,7 @@
         <v>135</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
@@ -7140,42 +7162,46 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7223,22 +7249,22 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -7252,10 +7278,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7263,7 +7289,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>77</v>
@@ -7278,13 +7304,13 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7335,10 +7361,10 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>77</v>
@@ -7364,10 +7390,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7390,13 +7416,13 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>175</v>
+        <v>99</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7447,7 +7473,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7476,10 +7502,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7487,7 +7513,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>77</v>
@@ -7502,13 +7528,13 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7535,34 +7561,34 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AA52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="AG52" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>77</v>
@@ -7588,10 +7614,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7599,32 +7625,30 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>307</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7649,13 +7673,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>20</v>
+        <v>365</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -7673,16 +7697,16 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>97</v>
@@ -7700,12 +7724,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7716,10 +7740,10 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>20</v>
@@ -7728,15 +7752,17 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>312</v>
+        <v>367</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -7785,22 +7811,22 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>314</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>20</v>
@@ -7814,21 +7840,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -7840,17 +7866,15 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -7899,22 +7923,22 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -7928,14 +7952,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>321</v>
+        <v>160</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7948,26 +7972,24 @@
         <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -8015,7 +8037,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8030,7 +8052,7 @@
         <v>135</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>20</v>
@@ -8044,42 +8066,46 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I57" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="J57" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>367</v>
+        <v>329</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
       </c>
@@ -8127,22 +8153,22 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>20</v>
@@ -8154,12 +8180,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8167,7 +8193,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>77</v>
@@ -8182,13 +8208,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8239,10 +8265,10 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>77</v>
@@ -8266,12 +8292,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8294,13 +8320,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8351,7 +8377,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8378,12 +8404,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8394,10 +8420,10 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>20</v>
@@ -8406,20 +8432,16 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>307</v>
+        <v>182</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8467,13 +8489,13 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
@@ -8496,10 +8518,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8510,7 +8532,7 @@
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8522,16 +8544,20 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>312</v>
+        <v>383</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
@@ -8579,22 +8605,22 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>314</v>
+        <v>382</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>20</v>
@@ -8608,21 +8634,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -8634,17 +8660,15 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -8693,22 +8717,22 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>20</v>
@@ -8722,14 +8746,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>321</v>
+        <v>160</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8742,26 +8766,24 @@
         <v>20</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
@@ -8809,7 +8831,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -8824,7 +8846,7 @@
         <v>135</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
@@ -8838,44 +8860,46 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>384</v>
+        <v>329</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>385</v>
+        <v>330</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
@@ -8899,13 +8923,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -8923,22 +8947,22 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>383</v>
+        <v>331</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>20</v>
@@ -8952,10 +8976,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8978,16 +9002,16 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>388</v>
+        <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9013,13 +9037,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>248</v>
+        <v>109</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>392</v>
+        <v>110</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>393</v>
+        <v>111</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9037,7 +9061,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9077,7 +9101,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>77</v>
@@ -9092,15 +9116,17 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>175</v>
+        <v>395</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9125,13 +9151,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>20</v>
+        <v>399</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -9152,7 +9178,7 @@
         <v>394</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>77</v>
@@ -9178,10 +9204,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9189,10 +9215,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -9204,13 +9230,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>307</v>
+        <v>182</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9261,13 +9287,13 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
@@ -9290,10 +9316,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9304,7 +9330,7 @@
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -9316,13 +9342,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>312</v>
+        <v>405</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>313</v>
+        <v>406</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9373,22 +9399,22 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>314</v>
+        <v>404</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>20</v>
@@ -9402,21 +9428,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -9428,17 +9454,15 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9487,22 +9511,22 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>20</v>
@@ -9516,14 +9540,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>321</v>
+        <v>160</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9536,26 +9560,24 @@
         <v>20</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>129</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>20</v>
       </c>
@@ -9603,7 +9625,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -9618,7 +9640,7 @@
         <v>135</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>20</v>
@@ -9632,42 +9654,46 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>404</v>
+        <v>329</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
       </c>
@@ -9715,22 +9741,22 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>403</v>
+        <v>331</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>20</v>
@@ -9744,10 +9770,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9770,13 +9796,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>407</v>
+        <v>105</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9827,7 +9853,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9856,10 +9882,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9867,13 +9893,13 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>20</v>
@@ -9882,13 +9908,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9939,16 +9965,16 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>97</v>
@@ -9966,18 +9992,130 @@
         <v>20</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN73">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AN74">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI72">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
